--- a/output/Daily_Route_Summary.xlsx
+++ b/output/Daily_Route_Summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>司機</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>司機標籤</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>天數</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>總站數</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>總服務時間_分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>總車程_分</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>總里程_km</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>總工時_分</t>
         </is>
@@ -471,23 +464,28 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>42</v>
-      </c>
       <c r="D2" t="n">
-        <v>421</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>98.28500000000001</v>
+        <v>373</v>
       </c>
       <c r="F2" t="n">
-        <v>44.3039</v>
+        <v>86.06</v>
       </c>
       <c r="G2" t="n">
-        <v>519.285</v>
+        <v>66.38</v>
+      </c>
+      <c r="H2" t="n">
+        <v>459.06</v>
       </c>
     </row>
     <row r="3">
@@ -496,23 +494,28 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>44</v>
-      </c>
       <c r="D3" t="n">
-        <v>416</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>106.9066666666667</v>
+        <v>392</v>
       </c>
       <c r="F3" t="n">
-        <v>40.63019999999999</v>
+        <v>136.15</v>
       </c>
       <c r="G3" t="n">
-        <v>522.9066666666666</v>
+        <v>76.01000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>528.15</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +524,28 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>44</v>
-      </c>
       <c r="D4" t="n">
-        <v>392</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>131.4333333333333</v>
+        <v>328</v>
       </c>
       <c r="F4" t="n">
-        <v>50.8422</v>
+        <v>184.25</v>
       </c>
       <c r="G4" t="n">
-        <v>523.4333333333334</v>
+        <v>86.20999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>512.25</v>
       </c>
     </row>
     <row r="5">
@@ -546,23 +554,28 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>46</v>
-      </c>
       <c r="D5" t="n">
-        <v>424</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>96.68166666666666</v>
+        <v>358</v>
       </c>
       <c r="F5" t="n">
-        <v>45.0961</v>
+        <v>113.16</v>
       </c>
       <c r="G5" t="n">
-        <v>520.6816666666666</v>
+        <v>75.78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>471.16</v>
       </c>
     </row>
     <row r="6">
@@ -571,23 +584,28 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
-        <v>38</v>
-      </c>
       <c r="D6" t="n">
-        <v>342</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>167.0416666666667</v>
+        <v>365</v>
       </c>
       <c r="F6" t="n">
-        <v>70.8763</v>
+        <v>157.62</v>
       </c>
       <c r="G6" t="n">
-        <v>509.0416666666666</v>
+        <v>102.86</v>
+      </c>
+      <c r="H6" t="n">
+        <v>522.62</v>
       </c>
     </row>
     <row r="7">
@@ -596,23 +614,28 @@
           <t>P01</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P01｜平鎮1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
-        <v>38</v>
-      </c>
       <c r="D7" t="n">
-        <v>384</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>137.8516666666667</v>
+        <v>438</v>
       </c>
       <c r="F7" t="n">
-        <v>62.8164</v>
+        <v>100.41</v>
       </c>
       <c r="G7" t="n">
-        <v>521.8516666666667</v>
+        <v>73.55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>538.41</v>
       </c>
     </row>
     <row r="8">
@@ -621,23 +644,28 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>40</v>
-      </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>100.0683333333333</v>
+        <v>404</v>
       </c>
       <c r="F8" t="n">
-        <v>44.31</v>
+        <v>106.02</v>
       </c>
       <c r="G8" t="n">
-        <v>532.0683333333334</v>
+        <v>72.27</v>
+      </c>
+      <c r="H8" t="n">
+        <v>510.02</v>
       </c>
     </row>
     <row r="9">
@@ -646,23 +674,28 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>40</v>
-      </c>
       <c r="D9" t="n">
-        <v>400</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>117.145</v>
+        <v>407</v>
       </c>
       <c r="F9" t="n">
-        <v>44.8769</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>517.145</v>
+        <v>51.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>492.24</v>
       </c>
     </row>
     <row r="10">
@@ -671,23 +704,28 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
-        <v>26</v>
-      </c>
       <c r="D10" t="n">
-        <v>423</v>
+        <v>39</v>
       </c>
       <c r="E10" t="n">
-        <v>64.18333333333334</v>
+        <v>368</v>
       </c>
       <c r="F10" t="n">
-        <v>29.4427</v>
+        <v>155.94</v>
       </c>
       <c r="G10" t="n">
-        <v>487.1833333333333</v>
+        <v>77.36</v>
+      </c>
+      <c r="H10" t="n">
+        <v>523.9400000000001</v>
       </c>
     </row>
     <row r="11">
@@ -696,23 +734,28 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
-        <v>40</v>
-      </c>
       <c r="D11" t="n">
-        <v>408</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>115.385</v>
+        <v>252</v>
       </c>
       <c r="F11" t="n">
-        <v>50.9301</v>
+        <v>143.2</v>
       </c>
       <c r="G11" t="n">
-        <v>523.385</v>
+        <v>111.61</v>
+      </c>
+      <c r="H11" t="n">
+        <v>395.2</v>
       </c>
     </row>
     <row r="12">
@@ -721,23 +764,28 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
-        <v>33</v>
-      </c>
       <c r="D12" t="n">
-        <v>380</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>117.0616666666667</v>
+        <v>388</v>
       </c>
       <c r="F12" t="n">
-        <v>54.0658</v>
+        <v>100.38</v>
       </c>
       <c r="G12" t="n">
-        <v>497.0616666666667</v>
+        <v>67.56999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>488.38</v>
       </c>
     </row>
     <row r="13">
@@ -746,23 +794,28 @@
           <t>P02</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P02｜平鎮2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>6</v>
       </c>
-      <c r="C13" t="n">
-        <v>37</v>
-      </c>
       <c r="D13" t="n">
-        <v>352</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>146.4266666666667</v>
+        <v>350</v>
       </c>
       <c r="F13" t="n">
-        <v>72.53360000000001</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>498.4266666666667</v>
+        <v>79.90000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>449.07</v>
       </c>
     </row>
     <row r="14">
@@ -771,23 +824,28 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>36</v>
-      </c>
       <c r="D14" t="n">
-        <v>386</v>
+        <v>37</v>
       </c>
       <c r="E14" t="n">
-        <v>122.0933333333333</v>
+        <v>376</v>
       </c>
       <c r="F14" t="n">
-        <v>69.7771</v>
+        <v>134.11</v>
       </c>
       <c r="G14" t="n">
-        <v>508.0933333333334</v>
+        <v>85.75</v>
+      </c>
+      <c r="H14" t="n">
+        <v>510.11</v>
       </c>
     </row>
     <row r="15">
@@ -796,23 +854,28 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="n">
-        <v>32</v>
-      </c>
       <c r="D15" t="n">
-        <v>400</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>106.8083333333333</v>
+        <v>264</v>
       </c>
       <c r="F15" t="n">
-        <v>49.7774</v>
+        <v>82.67</v>
       </c>
       <c r="G15" t="n">
-        <v>506.8083333333333</v>
+        <v>47.26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>346.67</v>
       </c>
     </row>
     <row r="16">
@@ -821,23 +884,28 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
-        <v>38</v>
-      </c>
       <c r="D16" t="n">
-        <v>432</v>
+        <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>87.42333333333333</v>
+        <v>408</v>
       </c>
       <c r="F16" t="n">
-        <v>39.3425</v>
+        <v>115.39</v>
       </c>
       <c r="G16" t="n">
-        <v>519.4233333333333</v>
+        <v>50.93</v>
+      </c>
+      <c r="H16" t="n">
+        <v>523.39</v>
       </c>
     </row>
     <row r="17">
@@ -846,23 +914,28 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="n">
-        <v>34</v>
-      </c>
       <c r="D17" t="n">
-        <v>432</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>103.0716666666667</v>
+        <v>408</v>
       </c>
       <c r="F17" t="n">
-        <v>42.9359</v>
+        <v>69.67</v>
       </c>
       <c r="G17" t="n">
-        <v>535.0716666666667</v>
+        <v>38.65</v>
+      </c>
+      <c r="H17" t="n">
+        <v>477.67</v>
       </c>
     </row>
     <row r="18">
@@ -871,23 +944,28 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
-        <v>34</v>
-      </c>
       <c r="D18" t="n">
-        <v>330</v>
+        <v>32</v>
       </c>
       <c r="E18" t="n">
-        <v>209.1716666666667</v>
+        <v>296</v>
       </c>
       <c r="F18" t="n">
-        <v>99.93780000000001</v>
+        <v>232.3</v>
       </c>
       <c r="G18" t="n">
-        <v>539.1716666666666</v>
+        <v>130.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>528.3</v>
       </c>
     </row>
     <row r="19">
@@ -896,23 +974,28 @@
           <t>P03</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P03｜平鎮3</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="n">
-        <v>16</v>
-      </c>
       <c r="D19" t="n">
-        <v>412</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>124.7816666666667</v>
+        <v>336</v>
       </c>
       <c r="F19" t="n">
-        <v>72.3265</v>
+        <v>113.47</v>
       </c>
       <c r="G19" t="n">
-        <v>536.7816666666666</v>
+        <v>78.03</v>
+      </c>
+      <c r="H19" t="n">
+        <v>449.47</v>
       </c>
     </row>
     <row r="20">
@@ -921,23 +1004,28 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="n">
-        <v>25</v>
-      </c>
       <c r="D20" t="n">
-        <v>368</v>
+        <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>128.6433333333333</v>
+        <v>381</v>
       </c>
       <c r="F20" t="n">
-        <v>97.5673</v>
+        <v>111.67</v>
       </c>
       <c r="G20" t="n">
-        <v>496.6433333333333</v>
+        <v>73.79000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>492.67</v>
       </c>
     </row>
     <row r="21">
@@ -946,23 +1034,28 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
-        <v>39</v>
-      </c>
       <c r="D21" t="n">
-        <v>420</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>88.14833333333333</v>
+        <v>352</v>
       </c>
       <c r="F21" t="n">
-        <v>45.4279</v>
+        <v>148.91</v>
       </c>
       <c r="G21" t="n">
-        <v>508.1483333333333</v>
+        <v>71.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>500.91</v>
       </c>
     </row>
     <row r="22">
@@ -971,23 +1064,28 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>3</v>
       </c>
-      <c r="C22" t="n">
-        <v>32</v>
-      </c>
       <c r="D22" t="n">
-        <v>390</v>
+        <v>26</v>
       </c>
       <c r="E22" t="n">
-        <v>80.80666666666666</v>
+        <v>360</v>
       </c>
       <c r="F22" t="n">
-        <v>48.0951</v>
+        <v>124.51</v>
       </c>
       <c r="G22" t="n">
-        <v>470.8066666666667</v>
+        <v>66.15000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>484.51</v>
       </c>
     </row>
     <row r="23">
@@ -996,23 +1094,28 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
-        <v>30</v>
-      </c>
       <c r="D23" t="n">
-        <v>408</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>123.2233333333333</v>
+        <v>436</v>
       </c>
       <c r="F23" t="n">
-        <v>64.78659999999999</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>531.2233333333334</v>
+        <v>73.70999999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>534.01</v>
       </c>
     </row>
     <row r="24">
@@ -1021,23 +1124,28 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>5</v>
       </c>
-      <c r="C24" t="n">
-        <v>49</v>
-      </c>
       <c r="D24" t="n">
-        <v>416</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>66.52500000000001</v>
+        <v>208</v>
       </c>
       <c r="F24" t="n">
-        <v>37.2833</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>482.525</v>
+        <v>61.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>279.9</v>
       </c>
     </row>
     <row r="25">
@@ -1046,23 +1154,28 @@
           <t>P04</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P04｜平鎮4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>6</v>
       </c>
-      <c r="C25" t="n">
-        <v>46</v>
-      </c>
       <c r="D25" t="n">
-        <v>400</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>78.56</v>
+        <v>360</v>
       </c>
       <c r="F25" t="n">
-        <v>43.5728</v>
+        <v>147.72</v>
       </c>
       <c r="G25" t="n">
-        <v>478.56</v>
+        <v>77.98</v>
+      </c>
+      <c r="H25" t="n">
+        <v>507.72</v>
       </c>
     </row>
     <row r="26">
@@ -1071,23 +1184,28 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="n">
-        <v>30</v>
-      </c>
       <c r="D26" t="n">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>68.08833333333334</v>
+        <v>352</v>
       </c>
       <c r="F26" t="n">
-        <v>38.3392</v>
+        <v>163.04</v>
       </c>
       <c r="G26" t="n">
-        <v>476.0883333333334</v>
+        <v>108.56</v>
+      </c>
+      <c r="H26" t="n">
+        <v>515.04</v>
       </c>
     </row>
     <row r="27">
@@ -1096,23 +1214,28 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="n">
-        <v>38</v>
-      </c>
       <c r="D27" t="n">
-        <v>384</v>
+        <v>22</v>
       </c>
       <c r="E27" t="n">
-        <v>136.1983333333333</v>
+        <v>256</v>
       </c>
       <c r="F27" t="n">
-        <v>72.79780000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>520.1983333333333</v>
+        <v>55.83</v>
+      </c>
+      <c r="H27" t="n">
+        <v>347.18</v>
       </c>
     </row>
     <row r="28">
@@ -1121,23 +1244,28 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="n">
-        <v>19</v>
-      </c>
       <c r="D28" t="n">
-        <v>376</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>79.49499999999999</v>
+        <v>432</v>
       </c>
       <c r="F28" t="n">
-        <v>46.9293</v>
+        <v>81.17</v>
       </c>
       <c r="G28" t="n">
-        <v>455.495</v>
+        <v>33.11</v>
+      </c>
+      <c r="H28" t="n">
+        <v>513.17</v>
       </c>
     </row>
     <row r="29">
@@ -1146,23 +1274,28 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
-        <v>36</v>
-      </c>
       <c r="D29" t="n">
-        <v>360</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>134.8283333333333</v>
+        <v>436</v>
       </c>
       <c r="F29" t="n">
-        <v>75.73350000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>494.8283333333333</v>
+        <v>53.64</v>
+      </c>
+      <c r="H29" t="n">
+        <v>533.1</v>
       </c>
     </row>
     <row r="30">
@@ -1171,23 +1304,28 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>5</v>
       </c>
-      <c r="C30" t="n">
-        <v>35</v>
-      </c>
       <c r="D30" t="n">
-        <v>358.5</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>176.8516666666667</v>
+        <v>426</v>
       </c>
       <c r="F30" t="n">
-        <v>98.9757</v>
+        <v>112.14</v>
       </c>
       <c r="G30" t="n">
-        <v>535.3516666666667</v>
+        <v>68.81999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>538.14</v>
       </c>
     </row>
     <row r="31">
@@ -1196,23 +1334,28 @@
           <t>P05</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P05｜平鎮5</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>6</v>
       </c>
-      <c r="C31" t="n">
-        <v>25</v>
-      </c>
       <c r="D31" t="n">
-        <v>408</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>93.39166666666667</v>
+        <v>248</v>
       </c>
       <c r="F31" t="n">
-        <v>56.5746</v>
+        <v>35.28</v>
       </c>
       <c r="G31" t="n">
-        <v>501.3916666666667</v>
+        <v>33.11</v>
+      </c>
+      <c r="H31" t="n">
+        <v>283.28</v>
       </c>
     </row>
     <row r="32">
@@ -1221,23 +1364,28 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" t="n">
-        <v>30</v>
-      </c>
       <c r="D32" t="n">
-        <v>352</v>
+        <v>42</v>
       </c>
       <c r="E32" t="n">
-        <v>148.9116666666667</v>
+        <v>421</v>
       </c>
       <c r="F32" t="n">
-        <v>71.5004</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>500.9116666666667</v>
+        <v>44.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>519.29</v>
       </c>
     </row>
     <row r="33">
@@ -1246,23 +1394,28 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>2</v>
       </c>
-      <c r="C33" t="n">
-        <v>33</v>
-      </c>
       <c r="D33" t="n">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>106.0183333333333</v>
+        <v>240</v>
       </c>
       <c r="F33" t="n">
-        <v>72.27369999999999</v>
+        <v>100.95</v>
       </c>
       <c r="G33" t="n">
-        <v>510.0183333333333</v>
+        <v>59.41</v>
+      </c>
+      <c r="H33" t="n">
+        <v>340.95</v>
       </c>
     </row>
     <row r="34">
@@ -1271,23 +1424,28 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>3</v>
       </c>
-      <c r="C34" t="n">
-        <v>19</v>
-      </c>
       <c r="D34" t="n">
-        <v>472</v>
+        <v>34</v>
       </c>
       <c r="E34" t="n">
-        <v>64.98333333333333</v>
+        <v>412</v>
       </c>
       <c r="F34" t="n">
-        <v>40.7712</v>
+        <v>119.82</v>
       </c>
       <c r="G34" t="n">
-        <v>536.9833333333333</v>
+        <v>54.12</v>
+      </c>
+      <c r="H34" t="n">
+        <v>531.8199999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1296,23 +1454,28 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
-        <v>23</v>
-      </c>
       <c r="D35" t="n">
-        <v>368</v>
+        <v>27</v>
       </c>
       <c r="E35" t="n">
-        <v>149.4183333333334</v>
+        <v>392</v>
       </c>
       <c r="F35" t="n">
-        <v>89.97580000000001</v>
+        <v>105.75</v>
       </c>
       <c r="G35" t="n">
-        <v>517.4183333333333</v>
+        <v>53.78</v>
+      </c>
+      <c r="H35" t="n">
+        <v>497.75</v>
       </c>
     </row>
     <row r="36">
@@ -1321,23 +1484,28 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>5</v>
       </c>
-      <c r="C36" t="n">
-        <v>33</v>
-      </c>
       <c r="D36" t="n">
-        <v>376</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>135.9933333333333</v>
+        <v>16</v>
       </c>
       <c r="F36" t="n">
-        <v>86.18730000000001</v>
+        <v>63.77</v>
       </c>
       <c r="G36" t="n">
-        <v>511.9933333333333</v>
+        <v>52.41</v>
+      </c>
+      <c r="H36" t="n">
+        <v>79.77000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1346,23 +1514,28 @@
           <t>P06</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P06｜平鎮6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>6</v>
       </c>
-      <c r="C37" t="n">
-        <v>37</v>
-      </c>
       <c r="D37" t="n">
-        <v>376</v>
+        <v>48</v>
       </c>
       <c r="E37" t="n">
-        <v>134.1133333333333</v>
+        <v>440</v>
       </c>
       <c r="F37" t="n">
-        <v>85.7529</v>
+        <v>82.64</v>
       </c>
       <c r="G37" t="n">
-        <v>510.1133333333333</v>
+        <v>43.55</v>
+      </c>
+      <c r="H37" t="n">
+        <v>522.64</v>
       </c>
     </row>
     <row r="38">
@@ -1371,23 +1544,28 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="n">
-        <v>23</v>
-      </c>
       <c r="D38" t="n">
-        <v>407</v>
+        <v>38</v>
       </c>
       <c r="E38" t="n">
-        <v>85.24166666666666</v>
+        <v>384</v>
       </c>
       <c r="F38" t="n">
-        <v>51.7988</v>
+        <v>136.2</v>
       </c>
       <c r="G38" t="n">
-        <v>492.2416666666667</v>
+        <v>72.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>520.2</v>
       </c>
     </row>
     <row r="39">
@@ -1396,23 +1574,28 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" t="n">
-        <v>46</v>
-      </c>
       <c r="D39" t="n">
-        <v>432</v>
+        <v>24</v>
       </c>
       <c r="E39" t="n">
-        <v>90.2</v>
+        <v>224</v>
       </c>
       <c r="F39" t="n">
-        <v>56.20480000000001</v>
+        <v>117.23</v>
       </c>
       <c r="G39" t="n">
-        <v>522.2</v>
+        <v>69.97</v>
+      </c>
+      <c r="H39" t="n">
+        <v>341.23</v>
       </c>
     </row>
     <row r="40">
@@ -1421,23 +1604,28 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" t="n">
-        <v>20</v>
-      </c>
       <c r="D40" t="n">
-        <v>320</v>
+        <v>38</v>
       </c>
       <c r="E40" t="n">
-        <v>93.71499999999999</v>
+        <v>432</v>
       </c>
       <c r="F40" t="n">
-        <v>64.16849999999999</v>
+        <v>87.42</v>
       </c>
       <c r="G40" t="n">
-        <v>413.715</v>
+        <v>39.34</v>
+      </c>
+      <c r="H40" t="n">
+        <v>519.42</v>
       </c>
     </row>
     <row r="41">
@@ -1446,23 +1634,28 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="n">
-        <v>25</v>
-      </c>
       <c r="D41" t="n">
-        <v>382.5</v>
+        <v>44</v>
       </c>
       <c r="E41" t="n">
-        <v>111.67</v>
+        <v>416</v>
       </c>
       <c r="F41" t="n">
-        <v>73.79000000000001</v>
+        <v>65.86</v>
       </c>
       <c r="G41" t="n">
-        <v>494.17</v>
+        <v>34.4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>481.86</v>
       </c>
     </row>
     <row r="42">
@@ -1471,23 +1664,28 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
         <v>5</v>
       </c>
-      <c r="C42" t="n">
-        <v>47</v>
-      </c>
       <c r="D42" t="n">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="E42" t="n">
-        <v>83.33166666666666</v>
+        <v>395</v>
       </c>
       <c r="F42" t="n">
-        <v>44.2564</v>
+        <v>129.56</v>
       </c>
       <c r="G42" t="n">
-        <v>531.3316666666667</v>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>524.5599999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1496,23 +1694,28 @@
           <t>P07</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P07｜平鎮7</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
         <v>6</v>
       </c>
-      <c r="C43" t="n">
-        <v>20</v>
-      </c>
       <c r="D43" t="n">
+        <v>17</v>
+      </c>
+      <c r="E43" t="n">
         <v>368</v>
       </c>
-      <c r="E43" t="n">
-        <v>91.235</v>
-      </c>
       <c r="F43" t="n">
-        <v>50.2545</v>
+        <v>105.26</v>
       </c>
       <c r="G43" t="n">
-        <v>459.235</v>
+        <v>80.70999999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>473.26</v>
       </c>
     </row>
     <row r="44">
@@ -1521,23 +1724,28 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="n">
-        <v>24</v>
-      </c>
       <c r="D44" t="n">
-        <v>344</v>
+        <v>44</v>
       </c>
       <c r="E44" t="n">
-        <v>160.2083333333333</v>
+        <v>416</v>
       </c>
       <c r="F44" t="n">
-        <v>75.3065</v>
+        <v>106.91</v>
       </c>
       <c r="G44" t="n">
-        <v>504.2083333333334</v>
+        <v>40.63</v>
+      </c>
+      <c r="H44" t="n">
+        <v>522.91</v>
       </c>
     </row>
     <row r="45">
@@ -1546,23 +1754,28 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>2</v>
       </c>
-      <c r="C45" t="n">
-        <v>38</v>
-      </c>
       <c r="D45" t="n">
-        <v>352</v>
+        <v>40</v>
       </c>
       <c r="E45" t="n">
-        <v>163.0416666666667</v>
+        <v>432</v>
       </c>
       <c r="F45" t="n">
-        <v>108.5573</v>
+        <v>101.09</v>
       </c>
       <c r="G45" t="n">
-        <v>515.0416666666666</v>
+        <v>44.42</v>
+      </c>
+      <c r="H45" t="n">
+        <v>533.09</v>
       </c>
     </row>
     <row r="46">
@@ -1571,23 +1784,28 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
         <v>3</v>
       </c>
-      <c r="C46" t="n">
-        <v>20</v>
-      </c>
       <c r="D46" t="n">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="E46" t="n">
-        <v>83.91666666666667</v>
+        <v>376</v>
       </c>
       <c r="F46" t="n">
-        <v>59.6673</v>
+        <v>148.91</v>
       </c>
       <c r="G46" t="n">
-        <v>291.9166666666667</v>
+        <v>113.79</v>
+      </c>
+      <c r="H46" t="n">
+        <v>524.91</v>
       </c>
     </row>
     <row r="47">
@@ -1596,23 +1814,28 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
         <v>4</v>
       </c>
-      <c r="C47" t="n">
-        <v>23</v>
-      </c>
       <c r="D47" t="n">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="E47" t="n">
-        <v>86.06333333333333</v>
+        <v>344</v>
       </c>
       <c r="F47" t="n">
-        <v>66.37869999999999</v>
+        <v>160.21</v>
       </c>
       <c r="G47" t="n">
-        <v>459.0633333333333</v>
+        <v>75.31</v>
+      </c>
+      <c r="H47" t="n">
+        <v>504.21</v>
       </c>
     </row>
     <row r="48">
@@ -1621,23 +1844,28 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
         <v>5</v>
       </c>
-      <c r="C48" t="n">
-        <v>31</v>
-      </c>
       <c r="D48" t="n">
-        <v>344</v>
+        <v>22</v>
       </c>
       <c r="E48" t="n">
-        <v>122.425</v>
+        <v>354</v>
       </c>
       <c r="F48" t="n">
-        <v>71.20399999999999</v>
+        <v>107.61</v>
       </c>
       <c r="G48" t="n">
-        <v>466.425</v>
+        <v>59.3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>461.61</v>
       </c>
     </row>
     <row r="49">
@@ -1646,23 +1874,28 @@
           <t>P08</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P08｜平鎮8</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
         <v>6</v>
       </c>
-      <c r="C49" t="n">
-        <v>31</v>
-      </c>
       <c r="D49" t="n">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="E49" t="n">
-        <v>150.3733333333333</v>
+        <v>376</v>
       </c>
       <c r="F49" t="n">
-        <v>79.38510000000001</v>
+        <v>162.88</v>
       </c>
       <c r="G49" t="n">
-        <v>510.3733333333333</v>
+        <v>113.36</v>
+      </c>
+      <c r="H49" t="n">
+        <v>538.88</v>
       </c>
     </row>
     <row r="50">
@@ -1671,23 +1904,28 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
         <v>1</v>
       </c>
-      <c r="C50" t="n">
-        <v>33</v>
-      </c>
       <c r="D50" t="n">
-        <v>383</v>
+        <v>44</v>
       </c>
       <c r="E50" t="n">
-        <v>121.46</v>
+        <v>392</v>
       </c>
       <c r="F50" t="n">
-        <v>69.3509</v>
+        <v>131.43</v>
       </c>
       <c r="G50" t="n">
-        <v>504.46</v>
+        <v>50.84</v>
+      </c>
+      <c r="H50" t="n">
+        <v>523.4300000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1696,23 +1934,28 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
         <v>2</v>
       </c>
-      <c r="C51" t="n">
-        <v>22</v>
-      </c>
       <c r="D51" t="n">
-        <v>442.5</v>
+        <v>40</v>
       </c>
       <c r="E51" t="n">
-        <v>96.815</v>
+        <v>400</v>
       </c>
       <c r="F51" t="n">
-        <v>73.27289999999999</v>
+        <v>117.14</v>
       </c>
       <c r="G51" t="n">
-        <v>539.3150000000001</v>
+        <v>44.88</v>
+      </c>
+      <c r="H51" t="n">
+        <v>517.14</v>
       </c>
     </row>
     <row r="52">
@@ -1721,23 +1964,28 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="n">
-        <v>40</v>
-      </c>
       <c r="D52" t="n">
-        <v>418</v>
+        <v>28</v>
       </c>
       <c r="E52" t="n">
-        <v>114.3933333333333</v>
+        <v>382</v>
       </c>
       <c r="F52" t="n">
-        <v>75.69810000000001</v>
+        <v>117.52</v>
       </c>
       <c r="G52" t="n">
-        <v>532.3933333333333</v>
+        <v>57.59</v>
+      </c>
+      <c r="H52" t="n">
+        <v>499.52</v>
       </c>
     </row>
     <row r="53">
@@ -1746,23 +1994,28 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
-        <v>26</v>
-      </c>
       <c r="D53" t="n">
-        <v>438</v>
+        <v>46</v>
       </c>
       <c r="E53" t="n">
-        <v>100.41</v>
+        <v>432</v>
       </c>
       <c r="F53" t="n">
-        <v>73.5502</v>
+        <v>90.2</v>
       </c>
       <c r="G53" t="n">
-        <v>538.41</v>
+        <v>56.2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>522.2</v>
       </c>
     </row>
     <row r="54">
@@ -1771,48 +2024,58 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P09｜平鎮9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>5</v>
       </c>
-      <c r="C54" t="n">
-        <v>33</v>
-      </c>
       <c r="D54" t="n">
-        <v>312</v>
+        <v>52</v>
       </c>
       <c r="E54" t="n">
-        <v>159.8066666666667</v>
+        <v>456</v>
       </c>
       <c r="F54" t="n">
-        <v>90.376</v>
+        <v>82.34</v>
       </c>
       <c r="G54" t="n">
-        <v>471.8066666666667</v>
+        <v>44.05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>538.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>P09</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>6</v>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>368</v>
+        <v>46</v>
       </c>
       <c r="E55" t="n">
-        <v>93.645</v>
+        <v>424</v>
       </c>
       <c r="F55" t="n">
-        <v>71.13380000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>461.645</v>
+        <v>45.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>520.6800000000001</v>
       </c>
     </row>
     <row r="56">
@@ -1821,23 +2084,28 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
       </c>
       <c r="C56" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>296</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>232.2983333333333</v>
+        <v>444</v>
       </c>
       <c r="F56" t="n">
-        <v>130.7217</v>
+        <v>81.09</v>
       </c>
       <c r="G56" t="n">
-        <v>528.2983333333333</v>
+        <v>65.09</v>
+      </c>
+      <c r="H56" t="n">
+        <v>525.09</v>
       </c>
     </row>
     <row r="57">
@@ -1846,23 +2114,28 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>2</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
       </c>
       <c r="C57" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>434</v>
+        <v>25</v>
       </c>
       <c r="E57" t="n">
-        <v>101.2466666666667</v>
+        <v>430</v>
       </c>
       <c r="F57" t="n">
-        <v>69.17280000000001</v>
+        <v>62.24</v>
       </c>
       <c r="G57" t="n">
-        <v>535.2466666666667</v>
+        <v>30.55</v>
+      </c>
+      <c r="H57" t="n">
+        <v>492.24</v>
       </c>
     </row>
     <row r="58">
@@ -1871,23 +2144,28 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>3</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
       </c>
       <c r="C58" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
-        <v>163.9783333333334</v>
+        <v>472</v>
       </c>
       <c r="F58" t="n">
-        <v>106.2651</v>
+        <v>64.98</v>
       </c>
       <c r="G58" t="n">
-        <v>536.9783333333334</v>
+        <v>40.77</v>
+      </c>
+      <c r="H58" t="n">
+        <v>536.98</v>
       </c>
     </row>
     <row r="59">
@@ -1896,23 +2174,28 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>4</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>344</v>
+        <v>27</v>
       </c>
       <c r="E59" t="n">
-        <v>94.125</v>
+        <v>400</v>
       </c>
       <c r="F59" t="n">
-        <v>75.0352</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>438.125</v>
+        <v>56.12</v>
+      </c>
+      <c r="H59" t="n">
+        <v>494.1</v>
       </c>
     </row>
     <row r="60">
@@ -1921,48 +2204,58 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>5</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P10｜平鎮10</t>
+        </is>
       </c>
       <c r="C60" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>376</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>162.8766666666667</v>
+        <v>40</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3579</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>538.8766666666667</v>
+        <v>84.53</v>
+      </c>
+      <c r="H60" t="n">
+        <v>117.51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>6</v>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
       </c>
       <c r="C61" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>395</v>
+        <v>38</v>
       </c>
       <c r="E61" t="n">
-        <v>129.5566666666667</v>
+        <v>342</v>
       </c>
       <c r="F61" t="n">
-        <v>92.90010000000001</v>
+        <v>167.04</v>
       </c>
       <c r="G61" t="n">
-        <v>524.5566666666666</v>
+        <v>70.88</v>
+      </c>
+      <c r="H61" t="n">
+        <v>509.04</v>
       </c>
     </row>
     <row r="62">
@@ -1971,23 +2264,28 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>1</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>378</v>
+        <v>23</v>
       </c>
       <c r="E62" t="n">
-        <v>94.10833333333333</v>
+        <v>368</v>
       </c>
       <c r="F62" t="n">
-        <v>77.2955</v>
+        <v>149.42</v>
       </c>
       <c r="G62" t="n">
-        <v>472.1083333333333</v>
+        <v>89.98</v>
+      </c>
+      <c r="H62" t="n">
+        <v>517.42</v>
       </c>
     </row>
     <row r="63">
@@ -1996,23 +2294,28 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>2</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
       </c>
       <c r="C63" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>388</v>
+        <v>39</v>
       </c>
       <c r="E63" t="n">
-        <v>131.3916666666667</v>
+        <v>386</v>
       </c>
       <c r="F63" t="n">
-        <v>90.07430000000001</v>
+        <v>123.53</v>
       </c>
       <c r="G63" t="n">
-        <v>519.3916666666667</v>
+        <v>70.48999999999999</v>
+      </c>
+      <c r="H63" t="n">
+        <v>509.53</v>
       </c>
     </row>
     <row r="64">
@@ -2021,23 +2324,28 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>3</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
       </c>
       <c r="C64" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>168</v>
+        <v>35</v>
       </c>
       <c r="E64" t="n">
-        <v>161.1533333333333</v>
+        <v>358.5</v>
       </c>
       <c r="F64" t="n">
-        <v>122.2114</v>
+        <v>176.85</v>
       </c>
       <c r="G64" t="n">
-        <v>329.1533333333333</v>
+        <v>98.98</v>
+      </c>
+      <c r="H64" t="n">
+        <v>535.35</v>
       </c>
     </row>
     <row r="65">
@@ -2046,173 +2354,208 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>4</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P11｜平鎮11</t>
+        </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E65" t="n">
-        <v>77.50500000000001</v>
+        <v>404</v>
       </c>
       <c r="F65" t="n">
-        <v>84.5264</v>
+        <v>120.86</v>
       </c>
       <c r="G65" t="n">
-        <v>117.505</v>
+        <v>58.27</v>
+      </c>
+      <c r="H65" t="n">
+        <v>524.86</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>5</v>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="E66" t="n">
-        <v>26.06333333333333</v>
+        <v>384</v>
       </c>
       <c r="F66" t="n">
-        <v>27.1061</v>
+        <v>137.85</v>
       </c>
       <c r="G66" t="n">
-        <v>134.0633333333333</v>
+        <v>62.82</v>
+      </c>
+      <c r="H66" t="n">
+        <v>521.85</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>6</v>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
         <v>16</v>
       </c>
-      <c r="E67" t="n">
-        <v>63.77333333333333</v>
-      </c>
       <c r="F67" t="n">
-        <v>52.4136</v>
+        <v>53.2</v>
       </c>
       <c r="G67" t="n">
-        <v>79.77333333333334</v>
+        <v>49.35</v>
+      </c>
+      <c r="H67" t="n">
+        <v>69.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>W01</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1</v>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
       </c>
       <c r="C68" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>357</v>
+        <v>26</v>
       </c>
       <c r="E68" t="n">
-        <v>104.7316666666667</v>
+        <v>423</v>
       </c>
       <c r="F68" t="n">
-        <v>50.2266</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>461.7316666666667</v>
+        <v>29.44</v>
+      </c>
+      <c r="H68" t="n">
+        <v>487.18</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>W01</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>2</v>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
       </c>
       <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="n">
         <v>37</v>
       </c>
-      <c r="D69" t="n">
-        <v>420</v>
-      </c>
       <c r="E69" t="n">
-        <v>85.81</v>
+        <v>416</v>
       </c>
       <c r="F69" t="n">
-        <v>38.56930000000001</v>
+        <v>54.7</v>
       </c>
       <c r="G69" t="n">
-        <v>505.81</v>
+        <v>27.09</v>
+      </c>
+      <c r="H69" t="n">
+        <v>470.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>W01</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>3</v>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
       </c>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>317</v>
+        <v>33</v>
       </c>
       <c r="E70" t="n">
-        <v>82.49333333333334</v>
+        <v>383</v>
       </c>
       <c r="F70" t="n">
-        <v>40.9318</v>
+        <v>121.46</v>
       </c>
       <c r="G70" t="n">
-        <v>399.4933333333333</v>
+        <v>69.34999999999999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>504.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>W01</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>4</v>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P12｜平鎮12</t>
+        </is>
       </c>
       <c r="C71" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>400</v>
+        <v>29</v>
       </c>
       <c r="E71" t="n">
-        <v>118.9116666666667</v>
+        <v>384</v>
       </c>
       <c r="F71" t="n">
-        <v>63.0069</v>
+        <v>125.2</v>
       </c>
       <c r="G71" t="n">
-        <v>518.9116666666666</v>
+        <v>76.13</v>
+      </c>
+      <c r="H71" t="n">
+        <v>509.2</v>
       </c>
     </row>
     <row r="72">
@@ -2221,23 +2564,28 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>5</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
       </c>
       <c r="C72" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>150.11</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>104.3071</v>
+        <v>14.07</v>
       </c>
       <c r="G72" t="n">
-        <v>406.11</v>
+        <v>8.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>22.07</v>
       </c>
     </row>
     <row r="73">
@@ -2246,98 +2594,118 @@
           <t>W01</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>6</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
       </c>
       <c r="C73" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>296</v>
+        <v>28</v>
       </c>
       <c r="E73" t="n">
-        <v>188.2583333333333</v>
+        <v>357</v>
       </c>
       <c r="F73" t="n">
-        <v>112.5843</v>
+        <v>104.73</v>
       </c>
       <c r="G73" t="n">
-        <v>484.2583333333333</v>
+        <v>50.23</v>
+      </c>
+      <c r="H73" t="n">
+        <v>461.73</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>W02</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>1</v>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>288</v>
+        <v>38</v>
       </c>
       <c r="E74" t="n">
-        <v>130.16</v>
+        <v>452</v>
       </c>
       <c r="F74" t="n">
-        <v>87.82260000000001</v>
+        <v>85.81</v>
       </c>
       <c r="G74" t="n">
-        <v>418.16</v>
+        <v>38.57</v>
+      </c>
+      <c r="H74" t="n">
+        <v>537.8099999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>W02</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>2</v>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
       </c>
       <c r="C75" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="E75" t="n">
-        <v>81.33500000000001</v>
+        <v>376</v>
       </c>
       <c r="F75" t="n">
-        <v>37.2708</v>
+        <v>137.65</v>
       </c>
       <c r="G75" t="n">
-        <v>361.335</v>
+        <v>84.75</v>
+      </c>
+      <c r="H75" t="n">
+        <v>513.65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>W02</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>3</v>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>W01｜五股1</t>
+        </is>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>82.57666666666667</v>
+        <v>280</v>
       </c>
       <c r="F76" t="n">
-        <v>45.9717</v>
+        <v>128.8</v>
       </c>
       <c r="G76" t="n">
-        <v>210.5766666666667</v>
+        <v>86.20999999999999</v>
+      </c>
+      <c r="H76" t="n">
+        <v>408.8</v>
       </c>
     </row>
     <row r="77">
@@ -2346,23 +2714,28 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>4</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
       </c>
       <c r="C77" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>426</v>
+        <v>27</v>
       </c>
       <c r="E77" t="n">
-        <v>101.6783333333333</v>
+        <v>280</v>
       </c>
       <c r="F77" t="n">
-        <v>50.0845</v>
+        <v>81.34</v>
       </c>
       <c r="G77" t="n">
-        <v>527.6783333333333</v>
+        <v>37.27</v>
+      </c>
+      <c r="H77" t="n">
+        <v>361.34</v>
       </c>
     </row>
     <row r="78">
@@ -2371,23 +2744,28 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>5</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="E78" t="n">
-        <v>25.79</v>
+        <v>296</v>
       </c>
       <c r="F78" t="n">
-        <v>15.886</v>
+        <v>188.26</v>
       </c>
       <c r="G78" t="n">
-        <v>141.79</v>
+        <v>112.58</v>
+      </c>
+      <c r="H78" t="n">
+        <v>484.26</v>
       </c>
     </row>
     <row r="79">
@@ -2396,23 +2774,58 @@
           <t>W02</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>6</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
       </c>
       <c r="C79" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>444</v>
+        <v>25</v>
       </c>
       <c r="E79" t="n">
-        <v>84.93166666666666</v>
+        <v>317</v>
       </c>
       <c r="F79" t="n">
-        <v>45.4319</v>
+        <v>90.27</v>
       </c>
       <c r="G79" t="n">
-        <v>528.9316666666666</v>
+        <v>44.02</v>
+      </c>
+      <c r="H79" t="n">
+        <v>407.27</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>W02｜五股2</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>18</v>
+      </c>
+      <c r="E80" t="n">
+        <v>256</v>
+      </c>
+      <c r="F80" t="n">
+        <v>152.39</v>
+      </c>
+      <c r="G80" t="n">
+        <v>105.84</v>
+      </c>
+      <c r="H80" t="n">
+        <v>408.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/Daily_Route_Summary.xlsx
+++ b/output/Daily_Route_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,19 +473,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F2" t="n">
-        <v>86.06</v>
+        <v>88.42</v>
       </c>
       <c r="G2" t="n">
-        <v>66.38</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>459.06</v>
+        <v>459.42</v>
       </c>
     </row>
     <row r="3">
@@ -533,19 +533,19 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>328</v>
+        <v>412</v>
       </c>
       <c r="F4" t="n">
-        <v>184.25</v>
+        <v>119.82</v>
       </c>
       <c r="G4" t="n">
-        <v>86.20999999999999</v>
+        <v>54.12</v>
       </c>
       <c r="H4" t="n">
-        <v>512.25</v>
+        <v>531.8199999999999</v>
       </c>
     </row>
     <row r="5">
@@ -563,19 +563,19 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>358</v>
+        <v>472</v>
       </c>
       <c r="F5" t="n">
-        <v>113.16</v>
+        <v>64.98</v>
       </c>
       <c r="G5" t="n">
-        <v>75.78</v>
+        <v>40.77</v>
       </c>
       <c r="H5" t="n">
-        <v>471.16</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="6">
@@ -593,49 +593,49 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="F6" t="n">
-        <v>157.62</v>
+        <v>120.86</v>
       </c>
       <c r="G6" t="n">
-        <v>102.86</v>
+        <v>58.27</v>
       </c>
       <c r="H6" t="n">
-        <v>522.62</v>
+        <v>524.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P01｜平鎮1</t>
+          <t>P02｜平鎮2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="F7" t="n">
-        <v>100.41</v>
+        <v>106.02</v>
       </c>
       <c r="G7" t="n">
-        <v>73.55</v>
+        <v>72.27</v>
       </c>
       <c r="H7" t="n">
-        <v>538.41</v>
+        <v>510.02</v>
       </c>
     </row>
     <row r="8">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F8" t="n">
-        <v>106.02</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>72.27</v>
+        <v>51.8</v>
       </c>
       <c r="H8" t="n">
-        <v>510.02</v>
+        <v>492.24</v>
       </c>
     </row>
     <row r="9">
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
-        <v>407</v>
+        <v>328</v>
       </c>
       <c r="F9" t="n">
-        <v>85.23999999999999</v>
+        <v>184.25</v>
       </c>
       <c r="G9" t="n">
-        <v>51.8</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>492.24</v>
+        <v>512.25</v>
       </c>
     </row>
     <row r="10">
@@ -710,22 +710,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>368</v>
+        <v>358.5</v>
       </c>
       <c r="F10" t="n">
-        <v>155.94</v>
+        <v>176.85</v>
       </c>
       <c r="G10" t="n">
-        <v>77.36</v>
+        <v>98.98</v>
       </c>
       <c r="H10" t="n">
-        <v>523.9400000000001</v>
+        <v>535.35</v>
       </c>
     </row>
     <row r="11">
@@ -740,82 +740,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>252</v>
+        <v>456</v>
       </c>
       <c r="F11" t="n">
-        <v>143.2</v>
+        <v>82.34</v>
       </c>
       <c r="G11" t="n">
-        <v>111.61</v>
+        <v>44.05</v>
       </c>
       <c r="H11" t="n">
-        <v>395.2</v>
+        <v>538.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P02｜平鎮2</t>
+          <t>P03｜平鎮3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F12" t="n">
-        <v>100.38</v>
+        <v>134.11</v>
       </c>
       <c r="G12" t="n">
-        <v>67.56999999999999</v>
+        <v>85.75</v>
       </c>
       <c r="H12" t="n">
-        <v>488.38</v>
+        <v>510.11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P02｜平鎮2</t>
+          <t>P03｜平鎮3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="F13" t="n">
-        <v>99.06999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="G13" t="n">
-        <v>79.90000000000001</v>
+        <v>50.25</v>
       </c>
       <c r="H13" t="n">
-        <v>449.07</v>
+        <v>459.23</v>
       </c>
     </row>
     <row r="14">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>376</v>
+        <v>423</v>
       </c>
       <c r="F14" t="n">
-        <v>134.11</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>85.75</v>
+        <v>29.44</v>
       </c>
       <c r="H14" t="n">
-        <v>510.11</v>
+        <v>487.18</v>
       </c>
     </row>
     <row r="15">
@@ -860,22 +860,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E15" t="n">
-        <v>264</v>
+        <v>416</v>
       </c>
       <c r="F15" t="n">
-        <v>82.67</v>
+        <v>54.7</v>
       </c>
       <c r="G15" t="n">
-        <v>47.26</v>
+        <v>27.09</v>
       </c>
       <c r="H15" t="n">
-        <v>346.67</v>
+        <v>470.7</v>
       </c>
     </row>
     <row r="16">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="F16" t="n">
-        <v>115.39</v>
+        <v>129.56</v>
       </c>
       <c r="G16" t="n">
-        <v>50.93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>523.39</v>
+        <v>524.5599999999999</v>
       </c>
     </row>
     <row r="17">
@@ -920,82 +920,82 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>408</v>
+        <v>368</v>
       </c>
       <c r="F17" t="n">
-        <v>69.67</v>
+        <v>105.26</v>
       </c>
       <c r="G17" t="n">
-        <v>38.65</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>477.67</v>
+        <v>473.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P03｜平鎮3</t>
+          <t>P04｜平鎮4</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>296</v>
+        <v>382.5</v>
       </c>
       <c r="F18" t="n">
-        <v>232.3</v>
+        <v>111.67</v>
       </c>
       <c r="G18" t="n">
-        <v>130.72</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>528.3</v>
+        <v>494.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P03｜平鎮3</t>
+          <t>P04｜平鎮4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="F19" t="n">
-        <v>113.47</v>
+        <v>148.91</v>
       </c>
       <c r="G19" t="n">
-        <v>78.03</v>
+        <v>71.5</v>
       </c>
       <c r="H19" t="n">
-        <v>449.47</v>
+        <v>500.91</v>
       </c>
     </row>
     <row r="20">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="F20" t="n">
-        <v>111.67</v>
+        <v>81.17</v>
       </c>
       <c r="G20" t="n">
-        <v>73.79000000000001</v>
+        <v>33.11</v>
       </c>
       <c r="H20" t="n">
-        <v>492.67</v>
+        <v>513.17</v>
       </c>
     </row>
     <row r="21">
@@ -1040,22 +1040,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>352</v>
+        <v>408</v>
       </c>
       <c r="F21" t="n">
-        <v>148.91</v>
+        <v>69.67</v>
       </c>
       <c r="G21" t="n">
-        <v>71.5</v>
+        <v>38.65</v>
       </c>
       <c r="H21" t="n">
-        <v>500.91</v>
+        <v>477.67</v>
       </c>
     </row>
     <row r="22">
@@ -1070,22 +1070,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>360</v>
+        <v>426</v>
       </c>
       <c r="F22" t="n">
-        <v>124.51</v>
+        <v>112.14</v>
       </c>
       <c r="G22" t="n">
-        <v>66.15000000000001</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>484.51</v>
+        <v>538.14</v>
       </c>
     </row>
     <row r="23">
@@ -1100,82 +1100,82 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>436</v>
+        <v>248</v>
       </c>
       <c r="F23" t="n">
-        <v>98.01000000000001</v>
+        <v>35.28</v>
       </c>
       <c r="G23" t="n">
-        <v>73.70999999999999</v>
+        <v>33.11</v>
       </c>
       <c r="H23" t="n">
-        <v>534.01</v>
+        <v>283.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P04｜平鎮4</t>
+          <t>P05｜平鎮5</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>208</v>
+        <v>352</v>
       </c>
       <c r="F24" t="n">
-        <v>71.90000000000001</v>
+        <v>163.04</v>
       </c>
       <c r="G24" t="n">
-        <v>61.1</v>
+        <v>108.56</v>
       </c>
       <c r="H24" t="n">
-        <v>279.9</v>
+        <v>515.04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P04｜平鎮4</t>
+          <t>P05｜平鎮5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="F25" t="n">
-        <v>147.72</v>
+        <v>112.1</v>
       </c>
       <c r="G25" t="n">
-        <v>77.98</v>
+        <v>64.23</v>
       </c>
       <c r="H25" t="n">
-        <v>507.72</v>
+        <v>456.1</v>
       </c>
     </row>
     <row r="26">
@@ -1190,22 +1190,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>352</v>
+        <v>408</v>
       </c>
       <c r="F26" t="n">
-        <v>163.04</v>
+        <v>115.39</v>
       </c>
       <c r="G26" t="n">
-        <v>108.56</v>
+        <v>50.93</v>
       </c>
       <c r="H26" t="n">
-        <v>515.04</v>
+        <v>523.39</v>
       </c>
     </row>
     <row r="27">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>256</v>
+        <v>436</v>
       </c>
       <c r="F27" t="n">
-        <v>91.18000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>55.83</v>
+        <v>53.64</v>
       </c>
       <c r="H27" t="n">
-        <v>347.18</v>
+        <v>533.1</v>
       </c>
     </row>
     <row r="28">
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>432</v>
+        <v>208</v>
       </c>
       <c r="F28" t="n">
-        <v>81.17</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>33.11</v>
+        <v>61.1</v>
       </c>
       <c r="H28" t="n">
-        <v>513.17</v>
+        <v>279.9</v>
       </c>
     </row>
     <row r="29">
@@ -1280,82 +1280,82 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>436</v>
+        <v>336</v>
       </c>
       <c r="F29" t="n">
-        <v>97.09999999999999</v>
+        <v>113.47</v>
       </c>
       <c r="G29" t="n">
-        <v>53.64</v>
+        <v>78.03</v>
       </c>
       <c r="H29" t="n">
-        <v>533.1</v>
+        <v>449.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P05｜平鎮5</t>
+          <t>P06｜平鎮6</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E30" t="n">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F30" t="n">
-        <v>112.14</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>68.81999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="H30" t="n">
-        <v>538.14</v>
+        <v>519.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P05｜平鎮5</t>
+          <t>P06｜平鎮6</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="F31" t="n">
-        <v>35.28</v>
+        <v>154.61</v>
       </c>
       <c r="G31" t="n">
-        <v>33.11</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>283.28</v>
+        <v>470.61</v>
       </c>
     </row>
     <row r="32">
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E32" t="n">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="F32" t="n">
-        <v>98.29000000000001</v>
+        <v>87.42</v>
       </c>
       <c r="G32" t="n">
-        <v>44.3</v>
+        <v>39.34</v>
       </c>
       <c r="H32" t="n">
-        <v>519.29</v>
+        <v>519.42</v>
       </c>
     </row>
     <row r="33">
@@ -1400,22 +1400,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E33" t="n">
-        <v>240</v>
+        <v>416</v>
       </c>
       <c r="F33" t="n">
-        <v>100.95</v>
+        <v>65.86</v>
       </c>
       <c r="G33" t="n">
-        <v>59.41</v>
+        <v>34.4</v>
       </c>
       <c r="H33" t="n">
-        <v>340.95</v>
+        <v>481.86</v>
       </c>
     </row>
     <row r="34">
@@ -1430,22 +1430,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E34" t="n">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="F34" t="n">
-        <v>119.82</v>
+        <v>100.38</v>
       </c>
       <c r="G34" t="n">
-        <v>54.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>531.8199999999999</v>
+        <v>488.38</v>
       </c>
     </row>
     <row r="35">
@@ -1460,82 +1460,82 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>392</v>
+        <v>350</v>
       </c>
       <c r="F35" t="n">
-        <v>105.75</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>53.78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>497.75</v>
+        <v>449.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>P06｜平鎮6</t>
+          <t>P07｜平鎮7</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E36" t="n">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="F36" t="n">
-        <v>63.77</v>
+        <v>136.2</v>
       </c>
       <c r="G36" t="n">
-        <v>52.41</v>
+        <v>72.8</v>
       </c>
       <c r="H36" t="n">
-        <v>79.77000000000001</v>
+        <v>520.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>P06｜平鎮6</t>
+          <t>P07｜平鎮7</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>440</v>
+        <v>308</v>
       </c>
       <c r="F37" t="n">
-        <v>82.64</v>
+        <v>105.49</v>
       </c>
       <c r="G37" t="n">
-        <v>43.55</v>
+        <v>81.12</v>
       </c>
       <c r="H37" t="n">
-        <v>522.64</v>
+        <v>413.49</v>
       </c>
     </row>
     <row r="38">
@@ -1550,22 +1550,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E38" t="n">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="F38" t="n">
-        <v>136.2</v>
+        <v>117.14</v>
       </c>
       <c r="G38" t="n">
-        <v>72.8</v>
+        <v>44.88</v>
       </c>
       <c r="H38" t="n">
-        <v>520.2</v>
+        <v>517.14</v>
       </c>
     </row>
     <row r="39">
@@ -1580,22 +1580,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
-        <v>224</v>
+        <v>376</v>
       </c>
       <c r="F39" t="n">
-        <v>117.23</v>
+        <v>148.91</v>
       </c>
       <c r="G39" t="n">
-        <v>69.97</v>
+        <v>113.79</v>
       </c>
       <c r="H39" t="n">
-        <v>341.23</v>
+        <v>524.91</v>
       </c>
     </row>
     <row r="40">
@@ -1610,22 +1610,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>432</v>
+        <v>16</v>
       </c>
       <c r="F40" t="n">
-        <v>87.42</v>
+        <v>63.77</v>
       </c>
       <c r="G40" t="n">
-        <v>39.34</v>
+        <v>52.41</v>
       </c>
       <c r="H40" t="n">
-        <v>519.42</v>
+        <v>79.77000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1640,82 +1640,82 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E41" t="n">
-        <v>416</v>
+        <v>360</v>
       </c>
       <c r="F41" t="n">
-        <v>65.86</v>
+        <v>147.72</v>
       </c>
       <c r="G41" t="n">
-        <v>34.4</v>
+        <v>77.98</v>
       </c>
       <c r="H41" t="n">
-        <v>481.86</v>
+        <v>507.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>P07｜平鎮7</t>
+          <t>P08｜平鎮8</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E42" t="n">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="F42" t="n">
-        <v>129.56</v>
+        <v>106.91</v>
       </c>
       <c r="G42" t="n">
-        <v>92.90000000000001</v>
+        <v>40.63</v>
       </c>
       <c r="H42" t="n">
-        <v>524.5599999999999</v>
+        <v>522.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>P07｜平鎮7</t>
+          <t>P08｜平鎮8</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>368</v>
+        <v>96</v>
       </c>
       <c r="F43" t="n">
-        <v>105.26</v>
+        <v>43.13</v>
       </c>
       <c r="G43" t="n">
-        <v>80.70999999999999</v>
+        <v>49.72</v>
       </c>
       <c r="H43" t="n">
-        <v>473.26</v>
+        <v>139.13</v>
       </c>
     </row>
     <row r="44">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="D44" t="n">
-        <v>44</v>
-      </c>
       <c r="E44" t="n">
-        <v>416</v>
+        <v>108</v>
       </c>
       <c r="F44" t="n">
-        <v>106.91</v>
+        <v>26.06</v>
       </c>
       <c r="G44" t="n">
-        <v>40.63</v>
+        <v>27.11</v>
       </c>
       <c r="H44" t="n">
-        <v>522.91</v>
+        <v>134.06</v>
       </c>
     </row>
     <row r="45">
@@ -1760,22 +1760,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E45" t="n">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F45" t="n">
-        <v>101.09</v>
+        <v>62.24</v>
       </c>
       <c r="G45" t="n">
-        <v>44.42</v>
+        <v>30.55</v>
       </c>
       <c r="H45" t="n">
-        <v>533.09</v>
+        <v>492.24</v>
       </c>
     </row>
     <row r="46">
@@ -1790,22 +1790,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E46" t="n">
-        <v>376</v>
+        <v>296</v>
       </c>
       <c r="F46" t="n">
-        <v>148.91</v>
+        <v>232.3</v>
       </c>
       <c r="G46" t="n">
-        <v>113.79</v>
+        <v>130.72</v>
       </c>
       <c r="H46" t="n">
-        <v>524.91</v>
+        <v>528.3</v>
       </c>
     </row>
     <row r="47">
@@ -1820,82 +1820,82 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E47" t="n">
-        <v>344</v>
+        <v>384</v>
       </c>
       <c r="F47" t="n">
-        <v>160.21</v>
+        <v>125.2</v>
       </c>
       <c r="G47" t="n">
-        <v>75.31</v>
+        <v>76.13</v>
       </c>
       <c r="H47" t="n">
-        <v>504.21</v>
+        <v>509.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>P08｜平鎮8</t>
+          <t>P09｜平鎮9</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E48" t="n">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="F48" t="n">
-        <v>107.61</v>
+        <v>131.43</v>
       </c>
       <c r="G48" t="n">
-        <v>59.3</v>
+        <v>50.84</v>
       </c>
       <c r="H48" t="n">
-        <v>461.61</v>
+        <v>523.4300000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P08｜平鎮8</t>
+          <t>P09｜平鎮9</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E49" t="n">
-        <v>376</v>
+        <v>432</v>
       </c>
       <c r="F49" t="n">
-        <v>162.88</v>
+        <v>101.09</v>
       </c>
       <c r="G49" t="n">
-        <v>113.36</v>
+        <v>44.42</v>
       </c>
       <c r="H49" t="n">
-        <v>538.88</v>
+        <v>533.09</v>
       </c>
     </row>
     <row r="50">
@@ -1910,22 +1910,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E50" t="n">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="F50" t="n">
-        <v>131.43</v>
+        <v>117.52</v>
       </c>
       <c r="G50" t="n">
-        <v>50.84</v>
+        <v>57.59</v>
       </c>
       <c r="H50" t="n">
-        <v>523.4300000000001</v>
+        <v>499.52</v>
       </c>
     </row>
     <row r="51">
@@ -1940,22 +1940,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E51" t="n">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="F51" t="n">
-        <v>117.14</v>
+        <v>90.2</v>
       </c>
       <c r="G51" t="n">
-        <v>44.88</v>
+        <v>56.2</v>
       </c>
       <c r="H51" t="n">
-        <v>517.14</v>
+        <v>522.2</v>
       </c>
     </row>
     <row r="52">
@@ -1970,82 +1970,82 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E52" t="n">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="F52" t="n">
-        <v>117.52</v>
+        <v>82.64</v>
       </c>
       <c r="G52" t="n">
-        <v>57.59</v>
+        <v>43.55</v>
       </c>
       <c r="H52" t="n">
-        <v>499.52</v>
+        <v>522.64</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>P09｜平鎮9</t>
+          <t>P10｜平鎮10</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>46</v>
       </c>
       <c r="E53" t="n">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="F53" t="n">
-        <v>90.2</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>56.2</v>
+        <v>45.1</v>
       </c>
       <c r="H53" t="n">
-        <v>522.2</v>
+        <v>520.6800000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>P09｜平鎮9</t>
+          <t>P10｜平鎮10</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E54" t="n">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="F54" t="n">
-        <v>82.34</v>
+        <v>99.05</v>
       </c>
       <c r="G54" t="n">
-        <v>44.05</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>538.34</v>
+        <v>529.05</v>
       </c>
     </row>
     <row r="55">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E55" t="n">
-        <v>424</v>
+        <v>368</v>
       </c>
       <c r="F55" t="n">
-        <v>96.68000000000001</v>
+        <v>155.94</v>
       </c>
       <c r="G55" t="n">
-        <v>45.1</v>
+        <v>77.36</v>
       </c>
       <c r="H55" t="n">
-        <v>520.6800000000001</v>
+        <v>523.9400000000001</v>
       </c>
     </row>
     <row r="56">
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E56" t="n">
-        <v>444</v>
+        <v>383</v>
       </c>
       <c r="F56" t="n">
-        <v>81.09</v>
+        <v>121.46</v>
       </c>
       <c r="G56" t="n">
-        <v>65.09</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>525.09</v>
+        <v>504.46</v>
       </c>
     </row>
     <row r="57">
@@ -2120,22 +2120,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E57" t="n">
-        <v>430</v>
+        <v>354</v>
       </c>
       <c r="F57" t="n">
-        <v>62.24</v>
+        <v>107.61</v>
       </c>
       <c r="G57" t="n">
-        <v>30.55</v>
+        <v>59.3</v>
       </c>
       <c r="H57" t="n">
-        <v>492.24</v>
+        <v>461.61</v>
       </c>
     </row>
     <row r="58">
@@ -2150,82 +2150,82 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E58" t="n">
-        <v>472</v>
+        <v>434</v>
       </c>
       <c r="F58" t="n">
-        <v>64.98</v>
+        <v>101.25</v>
       </c>
       <c r="G58" t="n">
-        <v>40.77</v>
+        <v>69.17</v>
       </c>
       <c r="H58" t="n">
-        <v>536.98</v>
+        <v>535.25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>P10｜平鎮10</t>
+          <t>P11｜平鎮11</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E59" t="n">
-        <v>400</v>
+        <v>342</v>
       </c>
       <c r="F59" t="n">
-        <v>94.09999999999999</v>
+        <v>167.04</v>
       </c>
       <c r="G59" t="n">
-        <v>56.12</v>
+        <v>70.88</v>
       </c>
       <c r="H59" t="n">
-        <v>494.1</v>
+        <v>509.04</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>P10｜平鎮10</t>
+          <t>P11｜平鎮11</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E60" t="n">
-        <v>40</v>
+        <v>368</v>
       </c>
       <c r="F60" t="n">
-        <v>77.51000000000001</v>
+        <v>149.42</v>
       </c>
       <c r="G60" t="n">
-        <v>84.53</v>
+        <v>89.98</v>
       </c>
       <c r="H60" t="n">
-        <v>117.51</v>
+        <v>517.42</v>
       </c>
     </row>
     <row r="61">
@@ -2240,22 +2240,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E61" t="n">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F61" t="n">
-        <v>167.04</v>
+        <v>124.51</v>
       </c>
       <c r="G61" t="n">
-        <v>70.88</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>509.04</v>
+        <v>484.51</v>
       </c>
     </row>
     <row r="62">
@@ -2270,22 +2270,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E62" t="n">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="F62" t="n">
-        <v>149.42</v>
+        <v>105.75</v>
       </c>
       <c r="G62" t="n">
-        <v>89.98</v>
+        <v>53.78</v>
       </c>
       <c r="H62" t="n">
-        <v>517.42</v>
+        <v>497.75</v>
       </c>
     </row>
     <row r="63">
@@ -2300,22 +2300,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E63" t="n">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="F63" t="n">
-        <v>123.53</v>
+        <v>157.62</v>
       </c>
       <c r="G63" t="n">
-        <v>70.48999999999999</v>
+        <v>102.86</v>
       </c>
       <c r="H63" t="n">
-        <v>509.53</v>
+        <v>522.62</v>
       </c>
     </row>
     <row r="64">
@@ -2330,52 +2330,52 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E64" t="n">
-        <v>358.5</v>
+        <v>442.5</v>
       </c>
       <c r="F64" t="n">
-        <v>176.85</v>
+        <v>96.81</v>
       </c>
       <c r="G64" t="n">
-        <v>98.98</v>
+        <v>73.27</v>
       </c>
       <c r="H64" t="n">
-        <v>535.35</v>
+        <v>539.3099999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>P11｜平鎮11</t>
+          <t>P12｜平鎮12</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E65" t="n">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="F65" t="n">
-        <v>120.86</v>
+        <v>137.85</v>
       </c>
       <c r="G65" t="n">
-        <v>58.27</v>
+        <v>62.82</v>
       </c>
       <c r="H65" t="n">
-        <v>524.86</v>
+        <v>521.85</v>
       </c>
     </row>
     <row r="66">
@@ -2390,22 +2390,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E66" t="n">
-        <v>384</v>
+        <v>336</v>
       </c>
       <c r="F66" t="n">
-        <v>137.85</v>
+        <v>196.22</v>
       </c>
       <c r="G66" t="n">
-        <v>62.82</v>
+        <v>140.76</v>
       </c>
       <c r="H66" t="n">
-        <v>521.85</v>
+        <v>532.22</v>
       </c>
     </row>
     <row r="67">
@@ -2420,22 +2420,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E67" t="n">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="F67" t="n">
-        <v>53.2</v>
+        <v>123.53</v>
       </c>
       <c r="G67" t="n">
-        <v>49.35</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>69.2</v>
+        <v>509.53</v>
       </c>
     </row>
     <row r="68">
@@ -2450,22 +2450,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E68" t="n">
-        <v>423</v>
+        <v>344</v>
       </c>
       <c r="F68" t="n">
-        <v>64.18000000000001</v>
+        <v>160.21</v>
       </c>
       <c r="G68" t="n">
-        <v>29.44</v>
+        <v>75.31</v>
       </c>
       <c r="H68" t="n">
-        <v>487.18</v>
+        <v>504.21</v>
       </c>
     </row>
     <row r="69">
@@ -2480,22 +2480,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E69" t="n">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="F69" t="n">
-        <v>54.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>27.09</v>
+        <v>56.12</v>
       </c>
       <c r="H69" t="n">
-        <v>470.7</v>
+        <v>494.1</v>
       </c>
     </row>
     <row r="70">
@@ -2510,52 +2510,52 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E70" t="n">
-        <v>383</v>
+        <v>168</v>
       </c>
       <c r="F70" t="n">
-        <v>121.46</v>
+        <v>161.15</v>
       </c>
       <c r="G70" t="n">
-        <v>69.34999999999999</v>
+        <v>122.21</v>
       </c>
       <c r="H70" t="n">
-        <v>504.46</v>
+        <v>329.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>W01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>P12｜平鎮12</t>
+          <t>W01｜五股1</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>384</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
-        <v>125.2</v>
+        <v>14.07</v>
       </c>
       <c r="G71" t="n">
-        <v>76.13</v>
+        <v>8.5</v>
       </c>
       <c r="H71" t="n">
-        <v>509.2</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="72">
@@ -2570,22 +2570,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>357</v>
       </c>
       <c r="F72" t="n">
-        <v>14.07</v>
+        <v>104.73</v>
       </c>
       <c r="G72" t="n">
-        <v>8.5</v>
+        <v>50.23</v>
       </c>
       <c r="H72" t="n">
-        <v>22.07</v>
+        <v>461.73</v>
       </c>
     </row>
     <row r="73">
@@ -2600,22 +2600,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E73" t="n">
-        <v>357</v>
+        <v>452</v>
       </c>
       <c r="F73" t="n">
-        <v>104.73</v>
+        <v>85.81</v>
       </c>
       <c r="G73" t="n">
-        <v>50.23</v>
+        <v>38.57</v>
       </c>
       <c r="H73" t="n">
-        <v>461.73</v>
+        <v>537.8099999999999</v>
       </c>
     </row>
     <row r="74">
@@ -2630,22 +2630,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E74" t="n">
-        <v>452</v>
+        <v>376</v>
       </c>
       <c r="F74" t="n">
-        <v>85.81</v>
+        <v>137.65</v>
       </c>
       <c r="G74" t="n">
-        <v>38.57</v>
+        <v>84.75</v>
       </c>
       <c r="H74" t="n">
-        <v>537.8099999999999</v>
+        <v>513.65</v>
       </c>
     </row>
     <row r="75">
@@ -2660,52 +2660,52 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>376</v>
+        <v>280</v>
       </c>
       <c r="F75" t="n">
-        <v>137.65</v>
+        <v>128.8</v>
       </c>
       <c r="G75" t="n">
-        <v>84.75</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>513.65</v>
+        <v>408.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>W01</t>
+          <t>W02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>W01｜五股1</t>
+          <t>W02｜五股2</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E76" t="n">
         <v>280</v>
       </c>
       <c r="F76" t="n">
-        <v>128.8</v>
+        <v>81.34</v>
       </c>
       <c r="G76" t="n">
-        <v>86.20999999999999</v>
+        <v>37.27</v>
       </c>
       <c r="H76" t="n">
-        <v>408.8</v>
+        <v>361.34</v>
       </c>
     </row>
     <row r="77">
@@ -2720,22 +2720,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E77" t="n">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="F77" t="n">
-        <v>81.34</v>
+        <v>188.26</v>
       </c>
       <c r="G77" t="n">
-        <v>37.27</v>
+        <v>112.58</v>
       </c>
       <c r="H77" t="n">
-        <v>361.34</v>
+        <v>484.26</v>
       </c>
     </row>
     <row r="78">
@@ -2750,22 +2750,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E78" t="n">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="F78" t="n">
-        <v>188.26</v>
+        <v>90.27</v>
       </c>
       <c r="G78" t="n">
-        <v>112.58</v>
+        <v>44.02</v>
       </c>
       <c r="H78" t="n">
-        <v>484.26</v>
+        <v>407.27</v>
       </c>
     </row>
     <row r="79">
@@ -2780,51 +2780,21 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E79" t="n">
-        <v>317</v>
+        <v>256</v>
       </c>
       <c r="F79" t="n">
-        <v>90.27</v>
+        <v>152.39</v>
       </c>
       <c r="G79" t="n">
-        <v>44.02</v>
+        <v>105.84</v>
       </c>
       <c r="H79" t="n">
-        <v>407.27</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>W02</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>W02｜五股2</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>4</v>
-      </c>
-      <c r="D80" t="n">
-        <v>18</v>
-      </c>
-      <c r="E80" t="n">
-        <v>256</v>
-      </c>
-      <c r="F80" t="n">
-        <v>152.39</v>
-      </c>
-      <c r="G80" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="H80" t="n">
         <v>408.39</v>
       </c>
     </row>

--- a/output/Daily_Route_Summary.xlsx
+++ b/output/Daily_Route_Summary.xlsx
@@ -473,19 +473,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F2" t="n">
-        <v>88.42</v>
+        <v>86.06</v>
       </c>
       <c r="G2" t="n">
-        <v>67.43000000000001</v>
+        <v>66.38</v>
       </c>
       <c r="H2" t="n">
-        <v>459.42</v>
+        <v>459.06</v>
       </c>
     </row>
     <row r="3">
@@ -533,19 +533,19 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="F4" t="n">
-        <v>119.82</v>
+        <v>81.17</v>
       </c>
       <c r="G4" t="n">
-        <v>54.12</v>
+        <v>33.11</v>
       </c>
       <c r="H4" t="n">
-        <v>531.8199999999999</v>
+        <v>513.17</v>
       </c>
     </row>
     <row r="5">
@@ -563,19 +563,19 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="F5" t="n">
-        <v>64.98</v>
+        <v>105.75</v>
       </c>
       <c r="G5" t="n">
-        <v>40.77</v>
+        <v>53.78</v>
       </c>
       <c r="H5" t="n">
-        <v>536.98</v>
+        <v>497.75</v>
       </c>
     </row>
     <row r="6">
@@ -593,49 +593,49 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>404</v>
+        <v>456</v>
       </c>
       <c r="F6" t="n">
-        <v>120.86</v>
+        <v>82.34</v>
       </c>
       <c r="G6" t="n">
-        <v>58.27</v>
+        <v>44.05</v>
       </c>
       <c r="H6" t="n">
-        <v>524.86</v>
+        <v>538.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P02｜平鎮2</t>
+          <t>P01｜平鎮1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="F7" t="n">
-        <v>106.02</v>
+        <v>101.25</v>
       </c>
       <c r="G7" t="n">
-        <v>72.27</v>
+        <v>69.17</v>
       </c>
       <c r="H7" t="n">
-        <v>510.02</v>
+        <v>535.25</v>
       </c>
     </row>
     <row r="8">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F8" t="n">
-        <v>85.23999999999999</v>
+        <v>106.02</v>
       </c>
       <c r="G8" t="n">
-        <v>51.8</v>
+        <v>72.27</v>
       </c>
       <c r="H8" t="n">
-        <v>492.24</v>
+        <v>510.02</v>
       </c>
     </row>
     <row r="9">
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>328</v>
+        <v>407</v>
       </c>
       <c r="F9" t="n">
-        <v>184.25</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>86.20999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="H9" t="n">
-        <v>512.25</v>
+        <v>492.24</v>
       </c>
     </row>
     <row r="10">
@@ -710,22 +710,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E10" t="n">
-        <v>358.5</v>
+        <v>368</v>
       </c>
       <c r="F10" t="n">
-        <v>176.85</v>
+        <v>155.94</v>
       </c>
       <c r="G10" t="n">
-        <v>98.98</v>
+        <v>77.36</v>
       </c>
       <c r="H10" t="n">
-        <v>535.35</v>
+        <v>523.9400000000001</v>
       </c>
     </row>
     <row r="11">
@@ -740,52 +740,52 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>456</v>
+        <v>296</v>
       </c>
       <c r="F11" t="n">
-        <v>82.34</v>
+        <v>232.3</v>
       </c>
       <c r="G11" t="n">
-        <v>44.05</v>
+        <v>130.72</v>
       </c>
       <c r="H11" t="n">
-        <v>538.34</v>
+        <v>528.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P03｜平鎮3</t>
+          <t>P02｜平鎮2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E12" t="n">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="F12" t="n">
-        <v>134.11</v>
+        <v>147.72</v>
       </c>
       <c r="G12" t="n">
-        <v>85.75</v>
+        <v>77.98</v>
       </c>
       <c r="H12" t="n">
-        <v>510.11</v>
+        <v>507.72</v>
       </c>
     </row>
     <row r="13">
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E13" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F13" t="n">
-        <v>91.23</v>
+        <v>134.11</v>
       </c>
       <c r="G13" t="n">
-        <v>50.25</v>
+        <v>85.75</v>
       </c>
       <c r="H13" t="n">
-        <v>459.23</v>
+        <v>510.11</v>
       </c>
     </row>
     <row r="14">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="F14" t="n">
-        <v>64.18000000000001</v>
+        <v>91.23</v>
       </c>
       <c r="G14" t="n">
-        <v>29.44</v>
+        <v>50.25</v>
       </c>
       <c r="H14" t="n">
-        <v>487.18</v>
+        <v>459.23</v>
       </c>
     </row>
     <row r="15">
@@ -860,22 +860,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F15" t="n">
-        <v>54.7</v>
+        <v>119.82</v>
       </c>
       <c r="G15" t="n">
-        <v>27.09</v>
+        <v>54.12</v>
       </c>
       <c r="H15" t="n">
-        <v>470.7</v>
+        <v>531.8199999999999</v>
       </c>
     </row>
     <row r="16">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
-        <v>395</v>
+        <v>358.5</v>
       </c>
       <c r="F16" t="n">
-        <v>129.56</v>
+        <v>176.85</v>
       </c>
       <c r="G16" t="n">
-        <v>92.90000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="H16" t="n">
-        <v>524.5599999999999</v>
+        <v>535.35</v>
       </c>
     </row>
     <row r="17">
@@ -920,52 +920,52 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="F17" t="n">
-        <v>105.26</v>
+        <v>107.61</v>
       </c>
       <c r="G17" t="n">
-        <v>80.70999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="H17" t="n">
-        <v>473.26</v>
+        <v>461.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P04｜平鎮4</t>
+          <t>P03｜平鎮3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" t="n">
-        <v>382.5</v>
+        <v>376</v>
       </c>
       <c r="F18" t="n">
-        <v>111.67</v>
+        <v>162.88</v>
       </c>
       <c r="G18" t="n">
-        <v>73.79000000000001</v>
+        <v>113.36</v>
       </c>
       <c r="H18" t="n">
-        <v>494.17</v>
+        <v>538.88</v>
       </c>
     </row>
     <row r="19">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
-        <v>352</v>
+        <v>382.5</v>
       </c>
       <c r="F19" t="n">
-        <v>148.91</v>
+        <v>111.67</v>
       </c>
       <c r="G19" t="n">
-        <v>71.5</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>500.91</v>
+        <v>494.17</v>
       </c>
     </row>
     <row r="20">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>432</v>
+        <v>352</v>
       </c>
       <c r="F20" t="n">
-        <v>81.17</v>
+        <v>148.91</v>
       </c>
       <c r="G20" t="n">
-        <v>33.11</v>
+        <v>71.5</v>
       </c>
       <c r="H20" t="n">
-        <v>513.17</v>
+        <v>500.91</v>
       </c>
     </row>
     <row r="21">
@@ -1040,22 +1040,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="F21" t="n">
-        <v>69.67</v>
+        <v>124.51</v>
       </c>
       <c r="G21" t="n">
-        <v>38.65</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>477.67</v>
+        <v>484.51</v>
       </c>
     </row>
     <row r="22">
@@ -1070,22 +1070,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="F22" t="n">
-        <v>112.14</v>
+        <v>69.67</v>
       </c>
       <c r="G22" t="n">
-        <v>68.81999999999999</v>
+        <v>38.65</v>
       </c>
       <c r="H22" t="n">
-        <v>538.14</v>
+        <v>477.67</v>
       </c>
     </row>
     <row r="23">
@@ -1100,52 +1100,52 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
-        <v>248</v>
+        <v>365</v>
       </c>
       <c r="F23" t="n">
-        <v>35.28</v>
+        <v>157.62</v>
       </c>
       <c r="G23" t="n">
-        <v>33.11</v>
+        <v>102.86</v>
       </c>
       <c r="H23" t="n">
-        <v>283.28</v>
+        <v>522.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P05｜平鎮5</t>
+          <t>P04｜平鎮4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>352</v>
+        <v>438</v>
       </c>
       <c r="F24" t="n">
-        <v>163.04</v>
+        <v>100.41</v>
       </c>
       <c r="G24" t="n">
-        <v>108.56</v>
+        <v>73.55</v>
       </c>
       <c r="H24" t="n">
-        <v>515.04</v>
+        <v>538.41</v>
       </c>
     </row>
     <row r="25">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E25" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F25" t="n">
-        <v>112.1</v>
+        <v>163.04</v>
       </c>
       <c r="G25" t="n">
-        <v>64.23</v>
+        <v>108.56</v>
       </c>
       <c r="H25" t="n">
-        <v>456.1</v>
+        <v>515.04</v>
       </c>
     </row>
     <row r="26">
@@ -1190,22 +1190,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E26" t="n">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="F26" t="n">
-        <v>115.39</v>
+        <v>112.1</v>
       </c>
       <c r="G26" t="n">
-        <v>50.93</v>
+        <v>64.23</v>
       </c>
       <c r="H26" t="n">
-        <v>523.39</v>
+        <v>456.1</v>
       </c>
     </row>
     <row r="27">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E27" t="n">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F27" t="n">
-        <v>97.09999999999999</v>
+        <v>87.42</v>
       </c>
       <c r="G27" t="n">
-        <v>53.64</v>
+        <v>39.34</v>
       </c>
       <c r="H27" t="n">
-        <v>533.1</v>
+        <v>519.42</v>
       </c>
     </row>
     <row r="28">
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>208</v>
+        <v>416</v>
       </c>
       <c r="F28" t="n">
-        <v>71.90000000000001</v>
+        <v>65.86</v>
       </c>
       <c r="G28" t="n">
-        <v>61.1</v>
+        <v>34.4</v>
       </c>
       <c r="H28" t="n">
-        <v>279.9</v>
+        <v>481.86</v>
       </c>
     </row>
     <row r="29">
@@ -1280,52 +1280,52 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>336</v>
+        <v>208</v>
       </c>
       <c r="F29" t="n">
-        <v>113.47</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>78.03</v>
+        <v>61.1</v>
       </c>
       <c r="H29" t="n">
-        <v>449.47</v>
+        <v>279.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P06｜平鎮6</t>
+          <t>P05｜平鎮5</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>421</v>
+        <v>248</v>
       </c>
       <c r="F30" t="n">
-        <v>98.29000000000001</v>
+        <v>35.28</v>
       </c>
       <c r="G30" t="n">
-        <v>44.3</v>
+        <v>33.11</v>
       </c>
       <c r="H30" t="n">
-        <v>519.29</v>
+        <v>283.28</v>
       </c>
     </row>
     <row r="31">
@@ -1340,22 +1340,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
-        <v>316</v>
+        <v>421</v>
       </c>
       <c r="F31" t="n">
-        <v>154.61</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>87.98999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="H31" t="n">
-        <v>470.61</v>
+        <v>519.29</v>
       </c>
     </row>
     <row r="32">
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E32" t="n">
-        <v>432</v>
+        <v>316</v>
       </c>
       <c r="F32" t="n">
-        <v>87.42</v>
+        <v>154.61</v>
       </c>
       <c r="G32" t="n">
-        <v>39.34</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>519.42</v>
+        <v>470.61</v>
       </c>
     </row>
     <row r="33">
@@ -1400,22 +1400,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E33" t="n">
-        <v>416</v>
+        <v>328</v>
       </c>
       <c r="F33" t="n">
-        <v>65.86</v>
+        <v>184.25</v>
       </c>
       <c r="G33" t="n">
-        <v>34.4</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>481.86</v>
+        <v>512.25</v>
       </c>
     </row>
     <row r="34">
@@ -1430,22 +1430,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
-        <v>388</v>
+        <v>472</v>
       </c>
       <c r="F34" t="n">
-        <v>100.38</v>
+        <v>64.98</v>
       </c>
       <c r="G34" t="n">
-        <v>67.56999999999999</v>
+        <v>40.77</v>
       </c>
       <c r="H34" t="n">
-        <v>488.38</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="35">
@@ -1460,22 +1460,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E35" t="n">
-        <v>350</v>
+        <v>440</v>
       </c>
       <c r="F35" t="n">
-        <v>99.06999999999999</v>
+        <v>82.64</v>
       </c>
       <c r="G35" t="n">
-        <v>79.90000000000001</v>
+        <v>43.55</v>
       </c>
       <c r="H35" t="n">
-        <v>449.07</v>
+        <v>522.64</v>
       </c>
     </row>
     <row r="36">
@@ -1553,19 +1553,19 @@
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>400</v>
+        <v>108</v>
       </c>
       <c r="F38" t="n">
-        <v>117.14</v>
+        <v>26.06</v>
       </c>
       <c r="G38" t="n">
-        <v>44.88</v>
+        <v>27.11</v>
       </c>
       <c r="H38" t="n">
-        <v>517.14</v>
+        <v>134.06</v>
       </c>
     </row>
     <row r="39">
@@ -1583,19 +1583,19 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E39" t="n">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="F39" t="n">
-        <v>148.91</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>113.79</v>
+        <v>53.64</v>
       </c>
       <c r="H39" t="n">
-        <v>524.91</v>
+        <v>533.1</v>
       </c>
     </row>
     <row r="40">
@@ -1613,19 +1613,19 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E40" t="n">
-        <v>16</v>
+        <v>426</v>
       </c>
       <c r="F40" t="n">
-        <v>63.77</v>
+        <v>112.14</v>
       </c>
       <c r="G40" t="n">
-        <v>52.41</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>79.77000000000001</v>
+        <v>538.14</v>
       </c>
     </row>
     <row r="41">
@@ -1643,19 +1643,19 @@
         <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F41" t="n">
-        <v>147.72</v>
+        <v>105.26</v>
       </c>
       <c r="G41" t="n">
-        <v>77.98</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>507.72</v>
+        <v>473.26</v>
       </c>
     </row>
     <row r="42">
@@ -1703,19 +1703,19 @@
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E43" t="n">
-        <v>96</v>
+        <v>423</v>
       </c>
       <c r="F43" t="n">
-        <v>43.13</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>49.72</v>
+        <v>29.44</v>
       </c>
       <c r="H43" t="n">
-        <v>139.13</v>
+        <v>487.18</v>
       </c>
     </row>
     <row r="44">
@@ -1733,19 +1733,19 @@
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E44" t="n">
-        <v>108</v>
+        <v>386</v>
       </c>
       <c r="F44" t="n">
-        <v>26.06</v>
+        <v>123.53</v>
       </c>
       <c r="G44" t="n">
-        <v>27.11</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>134.06</v>
+        <v>509.53</v>
       </c>
     </row>
     <row r="45">
@@ -1763,19 +1763,19 @@
         <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F45" t="n">
-        <v>62.24</v>
+        <v>90.2</v>
       </c>
       <c r="G45" t="n">
-        <v>30.55</v>
+        <v>56.2</v>
       </c>
       <c r="H45" t="n">
-        <v>492.24</v>
+        <v>522.2</v>
       </c>
     </row>
     <row r="46">
@@ -1793,19 +1793,19 @@
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E46" t="n">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="F46" t="n">
-        <v>232.3</v>
+        <v>125.2</v>
       </c>
       <c r="G46" t="n">
-        <v>130.72</v>
+        <v>76.13</v>
       </c>
       <c r="H46" t="n">
-        <v>528.3</v>
+        <v>509.2</v>
       </c>
     </row>
     <row r="47">
@@ -1823,19 +1823,19 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E47" t="n">
-        <v>384</v>
+        <v>168</v>
       </c>
       <c r="F47" t="n">
-        <v>125.2</v>
+        <v>161.15</v>
       </c>
       <c r="G47" t="n">
-        <v>76.13</v>
+        <v>122.21</v>
       </c>
       <c r="H47" t="n">
-        <v>509.2</v>
+        <v>329.15</v>
       </c>
     </row>
     <row r="48">
@@ -1886,16 +1886,16 @@
         <v>40</v>
       </c>
       <c r="E49" t="n">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="F49" t="n">
-        <v>101.09</v>
+        <v>115.39</v>
       </c>
       <c r="G49" t="n">
-        <v>44.42</v>
+        <v>50.93</v>
       </c>
       <c r="H49" t="n">
-        <v>533.09</v>
+        <v>523.39</v>
       </c>
     </row>
     <row r="50">
@@ -1913,19 +1913,19 @@
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E50" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F50" t="n">
-        <v>117.52</v>
+        <v>148.91</v>
       </c>
       <c r="G50" t="n">
-        <v>57.59</v>
+        <v>113.79</v>
       </c>
       <c r="H50" t="n">
-        <v>499.52</v>
+        <v>524.91</v>
       </c>
     </row>
     <row r="51">
@@ -1943,19 +1943,19 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>432</v>
+        <v>16</v>
       </c>
       <c r="F51" t="n">
-        <v>90.2</v>
+        <v>63.77</v>
       </c>
       <c r="G51" t="n">
-        <v>56.2</v>
+        <v>52.41</v>
       </c>
       <c r="H51" t="n">
-        <v>522.2</v>
+        <v>79.77000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -1973,49 +1973,49 @@
         <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E52" t="n">
-        <v>440</v>
+        <v>388</v>
       </c>
       <c r="F52" t="n">
-        <v>82.64</v>
+        <v>100.38</v>
       </c>
       <c r="G52" t="n">
-        <v>43.55</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>522.64</v>
+        <v>488.38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>P10｜平鎮10</t>
+          <t>P09｜平鎮9</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>424</v>
+        <v>350</v>
       </c>
       <c r="F53" t="n">
-        <v>96.68000000000001</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>45.1</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>520.6800000000001</v>
+        <v>449.07</v>
       </c>
     </row>
     <row r="54">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E54" t="n">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="F54" t="n">
-        <v>99.05</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>72.95999999999999</v>
+        <v>45.1</v>
       </c>
       <c r="H54" t="n">
-        <v>529.05</v>
+        <v>520.6800000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E55" t="n">
-        <v>368</v>
+        <v>432</v>
       </c>
       <c r="F55" t="n">
-        <v>155.94</v>
+        <v>101.09</v>
       </c>
       <c r="G55" t="n">
-        <v>77.36</v>
+        <v>44.42</v>
       </c>
       <c r="H55" t="n">
-        <v>523.9400000000001</v>
+        <v>533.09</v>
       </c>
     </row>
     <row r="56">
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E56" t="n">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="F56" t="n">
-        <v>121.46</v>
+        <v>54.7</v>
       </c>
       <c r="G56" t="n">
-        <v>69.34999999999999</v>
+        <v>27.09</v>
       </c>
       <c r="H56" t="n">
-        <v>504.46</v>
+        <v>470.7</v>
       </c>
     </row>
     <row r="57">
@@ -2120,22 +2120,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E57" t="n">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F57" t="n">
-        <v>107.61</v>
+        <v>160.21</v>
       </c>
       <c r="G57" t="n">
-        <v>59.3</v>
+        <v>75.31</v>
       </c>
       <c r="H57" t="n">
-        <v>461.61</v>
+        <v>504.21</v>
       </c>
     </row>
     <row r="58">
@@ -2150,22 +2150,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E58" t="n">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="F58" t="n">
-        <v>101.25</v>
+        <v>120.86</v>
       </c>
       <c r="G58" t="n">
-        <v>69.17</v>
+        <v>58.27</v>
       </c>
       <c r="H58" t="n">
-        <v>535.25</v>
+        <v>524.86</v>
       </c>
     </row>
     <row r="59">
@@ -2243,19 +2243,19 @@
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E61" t="n">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="F61" t="n">
-        <v>124.51</v>
+        <v>117.52</v>
       </c>
       <c r="G61" t="n">
-        <v>66.15000000000001</v>
+        <v>57.59</v>
       </c>
       <c r="H61" t="n">
-        <v>484.51</v>
+        <v>499.52</v>
       </c>
     </row>
     <row r="62">
@@ -2273,19 +2273,19 @@
         <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E62" t="n">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F62" t="n">
-        <v>105.75</v>
+        <v>121.46</v>
       </c>
       <c r="G62" t="n">
-        <v>53.78</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>497.75</v>
+        <v>504.46</v>
       </c>
     </row>
     <row r="63">
@@ -2303,19 +2303,19 @@
         <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E63" t="n">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="F63" t="n">
-        <v>157.62</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>102.86</v>
+        <v>56.12</v>
       </c>
       <c r="H63" t="n">
-        <v>522.62</v>
+        <v>494.1</v>
       </c>
     </row>
     <row r="64">
@@ -2393,19 +2393,19 @@
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E66" t="n">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="F66" t="n">
-        <v>196.22</v>
+        <v>117.14</v>
       </c>
       <c r="G66" t="n">
-        <v>140.76</v>
+        <v>44.88</v>
       </c>
       <c r="H66" t="n">
-        <v>532.22</v>
+        <v>517.14</v>
       </c>
     </row>
     <row r="67">
@@ -2423,19 +2423,19 @@
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E67" t="n">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="F67" t="n">
-        <v>123.53</v>
+        <v>62.24</v>
       </c>
       <c r="G67" t="n">
-        <v>70.48999999999999</v>
+        <v>30.55</v>
       </c>
       <c r="H67" t="n">
-        <v>509.53</v>
+        <v>492.24</v>
       </c>
     </row>
     <row r="68">
@@ -2453,19 +2453,19 @@
         <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E68" t="n">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="F68" t="n">
-        <v>160.21</v>
+        <v>129.56</v>
       </c>
       <c r="G68" t="n">
-        <v>75.31</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>504.21</v>
+        <v>524.5599999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2483,19 +2483,19 @@
         <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E69" t="n">
-        <v>400</v>
+        <v>336</v>
       </c>
       <c r="F69" t="n">
-        <v>94.09999999999999</v>
+        <v>113.47</v>
       </c>
       <c r="G69" t="n">
-        <v>56.12</v>
+        <v>78.03</v>
       </c>
       <c r="H69" t="n">
-        <v>494.1</v>
+        <v>449.47</v>
       </c>
     </row>
     <row r="70">
@@ -2513,19 +2513,19 @@
         <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="F70" t="n">
-        <v>161.15</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>122.21</v>
+        <v>84.53</v>
       </c>
       <c r="H70" t="n">
-        <v>329.15</v>
+        <v>117.51</v>
       </c>
     </row>
     <row r="71">

--- a/output/Daily_Route_Summary.xlsx
+++ b/output/Daily_Route_Summary.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,42 +429,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>司機</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>司機標籤</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>天數</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>總站數</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>總服務時間_分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>總車程_分</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>總里程_km</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>總工時_分</t>
         </is>
